--- a/Collections/India/#Republic_of_India#Commemorativer#[1964-present]#circulation_quality.xlsx
+++ b/Collections/India/#Republic_of_India#Commemorativer#[1964-present]#circulation_quality.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\India\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F412DC5F-4546-425E-80DA-547DAF97D8D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F54763C6-52F0-44B7-90F2-75A13F821326}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,6 +29,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -188,7 +191,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="957" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="965" uniqueCount="61">
   <si>
     <t>-</t>
   </si>
@@ -637,7 +640,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -706,11 +709,8 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -731,701 +731,19 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Обычный 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
-  <dxfs count="93">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="78">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1466,6 +784,574 @@
     </dxf>
     <dxf>
       <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1495,9 +1381,9 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="92"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="91" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="90"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="5" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -1800,7 +1686,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3001186-9460-468F-8F8C-A3E080BA5200}">
-  <dimension ref="A1:P88"/>
+  <dimension ref="A1:P89"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" customWidth="1"/>
@@ -1814,31 +1700,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="25" t="s">
         <v>3</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="22"/>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="29"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="31" t="s">
+      <c r="E1" s="28"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="24" t="s">
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="33"/>
     </row>
     <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="27"/>
+      <c r="A2" s="26"/>
       <c r="B2" s="18" t="s">
         <v>7</v>
       </c>
@@ -5792,6 +5678,52 @@
       </c>
       <c r="O88" s="16" t="str">
         <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="89" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A89" s="24">
+        <v>2025</v>
+      </c>
+      <c r="B89" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C89" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="D89" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E89" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="F89" s="12"/>
+      <c r="G89" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H89" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I89" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J89" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K89" s="4">
+        <v>0</v>
+      </c>
+      <c r="L89" s="4">
+        <v>0</v>
+      </c>
+      <c r="M89" s="4">
+        <v>0</v>
+      </c>
+      <c r="N89" s="4">
+        <v>0</v>
+      </c>
+      <c r="O89" s="16" t="str">
+        <f t="shared" ref="O89" si="3">IF(OR(AND(K89&gt;1,K89&lt;&gt;"-"),AND(L89&gt;1,L89&lt;&gt;"-"),AND(M89&gt;1,M89&lt;&gt;"-"),AND(N89&gt;1,N89&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -5804,7 +5736,7 @@
     <mergeCell ref="K1:N1"/>
   </mergeCells>
   <conditionalFormatting sqref="M10">
-    <cfRule type="colorScale" priority="180">
+    <cfRule type="colorScale" priority="188">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -5816,7 +5748,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L10">
-    <cfRule type="colorScale" priority="182">
+    <cfRule type="colorScale" priority="190">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -5828,16 +5760,113 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L10">
-    <cfRule type="containsText" dxfId="89" priority="181" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="77" priority="189" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M10">
-    <cfRule type="containsText" dxfId="88" priority="179" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="76" priority="187" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M16">
+    <cfRule type="colorScale" priority="176">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L16">
+    <cfRule type="colorScale" priority="178">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L16">
+    <cfRule type="containsText" dxfId="75" priority="177" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M16">
+    <cfRule type="containsText" dxfId="74" priority="175" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M33">
+    <cfRule type="colorScale" priority="172">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L33">
+    <cfRule type="colorScale" priority="174">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L33">
+    <cfRule type="containsText" dxfId="73" priority="173" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M33">
+    <cfRule type="containsText" dxfId="72" priority="171" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K33">
+    <cfRule type="colorScale" priority="170">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K33">
+    <cfRule type="containsText" dxfId="71" priority="169" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M35">
+    <cfRule type="colorScale" priority="166">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L35">
     <cfRule type="colorScale" priority="168">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5849,29 +5878,17 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L16">
-    <cfRule type="colorScale" priority="170">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L16">
-    <cfRule type="containsText" dxfId="87" priority="169" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M16">
-    <cfRule type="containsText" dxfId="86" priority="167" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M33">
+  <conditionalFormatting sqref="L35">
+    <cfRule type="containsText" dxfId="70" priority="167" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M35">
+    <cfRule type="containsText" dxfId="69" priority="165" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K35">
     <cfRule type="colorScale" priority="164">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5883,29 +5900,24 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L33">
-    <cfRule type="colorScale" priority="166">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L33">
-    <cfRule type="containsText" dxfId="85" priority="165" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M33">
-    <cfRule type="containsText" dxfId="84" priority="163" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K33">
+  <conditionalFormatting sqref="K35">
+    <cfRule type="containsText" dxfId="68" priority="163" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M37">
+    <cfRule type="colorScale" priority="160">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L37">
     <cfRule type="colorScale" priority="162">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5917,12 +5929,17 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K33">
-    <cfRule type="containsText" dxfId="83" priority="161" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M35">
+  <conditionalFormatting sqref="L37">
+    <cfRule type="containsText" dxfId="67" priority="161" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M37">
+    <cfRule type="containsText" dxfId="66" priority="159" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K37">
     <cfRule type="colorScale" priority="158">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5934,29 +5951,24 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L35">
-    <cfRule type="colorScale" priority="160">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L35">
-    <cfRule type="containsText" dxfId="82" priority="159" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M35">
-    <cfRule type="containsText" dxfId="81" priority="157" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K35">
+  <conditionalFormatting sqref="K37">
+    <cfRule type="containsText" dxfId="65" priority="157" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L39">
+    <cfRule type="colorScale" priority="148">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L38">
     <cfRule type="colorScale" priority="156">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5968,12 +5980,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K35">
-    <cfRule type="containsText" dxfId="80" priority="155" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M37">
+  <conditionalFormatting sqref="L38">
+    <cfRule type="containsText" dxfId="64" priority="155" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K38">
     <cfRule type="colorScale" priority="152">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5985,29 +5997,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L37">
-    <cfRule type="colorScale" priority="154">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L37">
-    <cfRule type="containsText" dxfId="79" priority="153" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M37">
-    <cfRule type="containsText" dxfId="78" priority="151" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K37">
+  <conditionalFormatting sqref="K38">
+    <cfRule type="containsText" dxfId="63" priority="151" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N38">
     <cfRule type="colorScale" priority="150">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6019,12 +6014,90 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K37">
-    <cfRule type="containsText" dxfId="77" priority="149" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+  <conditionalFormatting sqref="N38">
+    <cfRule type="containsText" dxfId="62" priority="149" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K39">
+    <cfRule type="containsText" dxfId="61" priority="143" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K42">
+    <cfRule type="containsText" dxfId="60" priority="131" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M39">
+    <cfRule type="colorScale" priority="146">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L43">
+    <cfRule type="colorScale" priority="130">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L39">
+    <cfRule type="containsText" dxfId="59" priority="147" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M39">
+    <cfRule type="containsText" dxfId="58" priority="145" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K39">
+    <cfRule type="colorScale" priority="144">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K43">
+    <cfRule type="containsText" dxfId="57" priority="125" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K42">
+    <cfRule type="colorScale" priority="132">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K41">
+    <cfRule type="containsText" dxfId="56" priority="137" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M41">
     <cfRule type="colorScale" priority="140">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6036,68 +6109,17 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L38">
-    <cfRule type="colorScale" priority="148">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L38">
-    <cfRule type="containsText" dxfId="76" priority="147" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K38">
-    <cfRule type="colorScale" priority="144">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K38">
-    <cfRule type="containsText" dxfId="74" priority="143" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N38">
-    <cfRule type="colorScale" priority="142">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N38">
-    <cfRule type="containsText" dxfId="73" priority="141" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K39">
-    <cfRule type="containsText" dxfId="72" priority="135" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K42">
-    <cfRule type="containsText" dxfId="70" priority="123" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M39">
+  <conditionalFormatting sqref="L44">
+    <cfRule type="containsText" dxfId="55" priority="123" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M41">
+    <cfRule type="containsText" dxfId="54" priority="139" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K41">
     <cfRule type="colorScale" priority="138">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6109,7 +6131,53 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="K43">
+    <cfRule type="colorScale" priority="126">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K44">
+    <cfRule type="containsText" dxfId="53" priority="121" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L44">
+    <cfRule type="colorScale" priority="124">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="L43">
+    <cfRule type="containsText" dxfId="52" priority="129" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K45">
+    <cfRule type="colorScale" priority="118">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K44">
     <cfRule type="colorScale" priority="122">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6121,102 +6189,41 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L39">
-    <cfRule type="containsText" dxfId="69" priority="139" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M39">
-    <cfRule type="containsText" dxfId="68" priority="137" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K39">
-    <cfRule type="colorScale" priority="136">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K43">
-    <cfRule type="containsText" dxfId="67" priority="117" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K42">
-    <cfRule type="colorScale" priority="124">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K41">
-    <cfRule type="containsText" dxfId="66" priority="129" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M41">
-    <cfRule type="colorScale" priority="132">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L44">
-    <cfRule type="containsText" dxfId="65" priority="115" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M41">
-    <cfRule type="containsText" dxfId="64" priority="131" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K41">
-    <cfRule type="colorScale" priority="130">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K43">
-    <cfRule type="colorScale" priority="118">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K44">
-    <cfRule type="containsText" dxfId="63" priority="113" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L44">
+  <conditionalFormatting sqref="K45">
+    <cfRule type="containsText" dxfId="51" priority="117" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L45">
+    <cfRule type="colorScale" priority="120">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L47">
+    <cfRule type="containsText" dxfId="50" priority="111" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K58">
+    <cfRule type="colorScale" priority="66">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L46">
     <cfRule type="colorScale" priority="116">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6228,58 +6235,97 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L43">
-    <cfRule type="containsText" dxfId="62" priority="121" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K45">
-    <cfRule type="colorScale" priority="110">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K44">
-    <cfRule type="colorScale" priority="114">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K45">
-    <cfRule type="containsText" dxfId="60" priority="109" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+  <conditionalFormatting sqref="K47">
+    <cfRule type="containsText" dxfId="49" priority="107" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K58">
+    <cfRule type="containsText" dxfId="48" priority="65" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L47">
+    <cfRule type="colorScale" priority="112">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K49">
+    <cfRule type="containsText" dxfId="47" priority="103" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L49">
+    <cfRule type="colorScale" priority="106">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L45">
-    <cfRule type="colorScale" priority="112">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L47">
-    <cfRule type="containsText" dxfId="59" priority="103" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K58">
+    <cfRule type="containsText" dxfId="46" priority="119" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K47">
+    <cfRule type="colorScale" priority="108">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M60">
+    <cfRule type="containsText" dxfId="45" priority="55" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L50">
+    <cfRule type="colorScale" priority="102">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L46">
+    <cfRule type="containsText" dxfId="44" priority="115" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K49">
+    <cfRule type="colorScale" priority="104">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K60">
     <cfRule type="colorScale" priority="58">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6291,46 +6337,80 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L46">
-    <cfRule type="colorScale" priority="108">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K47">
-    <cfRule type="containsText" dxfId="57" priority="99" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K58">
-    <cfRule type="containsText" dxfId="56" priority="57" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L47">
-    <cfRule type="colorScale" priority="104">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K49">
-    <cfRule type="containsText" dxfId="55" priority="95" operator="containsText" text="*-">
+  <conditionalFormatting sqref="N60">
+    <cfRule type="colorScale" priority="60">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N60">
+    <cfRule type="containsText" dxfId="43" priority="59" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M60">
+    <cfRule type="colorScale" priority="56">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K63">
+    <cfRule type="containsText" dxfId="42" priority="51" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L49">
+    <cfRule type="containsText" dxfId="41" priority="105" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M67">
+    <cfRule type="containsText" dxfId="40" priority="37" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L63">
+    <cfRule type="colorScale" priority="54">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L50">
+    <cfRule type="containsText" dxfId="39" priority="101" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K63">
+    <cfRule type="colorScale" priority="52">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M52">
     <cfRule type="colorScale" priority="98">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6342,29 +6422,36 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L45">
-    <cfRule type="containsText" dxfId="54" priority="111" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K47">
-    <cfRule type="colorScale" priority="100">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M60">
-    <cfRule type="containsText" dxfId="53" priority="47" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L50">
+  <conditionalFormatting sqref="M52">
+    <cfRule type="containsText" dxfId="38" priority="97" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M67">
+    <cfRule type="colorScale" priority="38">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M53">
+    <cfRule type="colorScale" priority="92">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L53">
     <cfRule type="colorScale" priority="94">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6376,13 +6463,222 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L46">
-    <cfRule type="containsText" dxfId="52" priority="107" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K49">
-    <cfRule type="colorScale" priority="96">
+  <conditionalFormatting sqref="L53">
+    <cfRule type="containsText" dxfId="37" priority="93" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M53">
+    <cfRule type="containsText" dxfId="36" priority="91" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K53">
+    <cfRule type="colorScale" priority="90">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K53">
+    <cfRule type="containsText" dxfId="35" priority="89" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L54">
+    <cfRule type="colorScale" priority="88">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L54">
+    <cfRule type="containsText" dxfId="34" priority="87" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L55">
+    <cfRule type="colorScale" priority="82">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L55">
+    <cfRule type="containsText" dxfId="33" priority="81" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N55">
+    <cfRule type="colorScale" priority="80">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N55">
+    <cfRule type="containsText" dxfId="32" priority="79" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L56">
+    <cfRule type="colorScale" priority="78">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L56">
+    <cfRule type="containsText" dxfId="31" priority="77" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N56">
+    <cfRule type="colorScale" priority="76">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N56">
+    <cfRule type="containsText" dxfId="30" priority="75" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K56">
+    <cfRule type="colorScale" priority="74">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K56">
+    <cfRule type="containsText" dxfId="29" priority="73" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M56">
+    <cfRule type="colorScale" priority="72">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M56">
+    <cfRule type="containsText" dxfId="28" priority="71" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L58">
+    <cfRule type="colorScale" priority="70">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L58">
+    <cfRule type="containsText" dxfId="27" priority="69" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N58">
+    <cfRule type="colorScale" priority="68">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N58">
+    <cfRule type="containsText" dxfId="26" priority="67" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K65">
+    <cfRule type="colorScale" priority="48">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K65">
+    <cfRule type="containsText" dxfId="25" priority="47" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M58">
+    <cfRule type="colorScale" priority="64">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M58">
+    <cfRule type="containsText" dxfId="24" priority="63" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K66">
+    <cfRule type="colorScale" priority="44">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -6394,6 +6690,21 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K60">
+    <cfRule type="containsText" dxfId="23" priority="57" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K66">
+    <cfRule type="containsText" dxfId="22" priority="43" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L63">
+    <cfRule type="containsText" dxfId="21" priority="53" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L65">
     <cfRule type="colorScale" priority="50">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6405,51 +6716,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N60">
-    <cfRule type="colorScale" priority="52">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N60">
-    <cfRule type="containsText" dxfId="51" priority="51" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M60">
-    <cfRule type="colorScale" priority="48">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K63">
-    <cfRule type="containsText" dxfId="49" priority="43" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L49">
-    <cfRule type="containsText" dxfId="48" priority="97" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M67">
-    <cfRule type="containsText" dxfId="47" priority="29" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L63">
+  <conditionalFormatting sqref="L65">
+    <cfRule type="containsText" dxfId="20" priority="49" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L66">
     <cfRule type="colorScale" priority="46">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6461,41 +6733,63 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L50">
-    <cfRule type="containsText" dxfId="46" priority="93" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K63">
-    <cfRule type="colorScale" priority="44">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M52">
-    <cfRule type="colorScale" priority="90">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M52">
-    <cfRule type="containsText" dxfId="43" priority="89" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M67">
+  <conditionalFormatting sqref="L66">
+    <cfRule type="containsText" dxfId="19" priority="45" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K73">
+    <cfRule type="containsText" dxfId="18" priority="33" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L73">
+    <cfRule type="colorScale" priority="36">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K73">
+    <cfRule type="colorScale" priority="34">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L73">
+    <cfRule type="containsText" dxfId="17" priority="35" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N73">
+    <cfRule type="colorScale" priority="32">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N73">
+    <cfRule type="containsText" dxfId="16" priority="31" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L86">
     <cfRule type="colorScale" priority="30">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6507,340 +6801,17 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M53">
-    <cfRule type="colorScale" priority="84">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L53">
-    <cfRule type="colorScale" priority="86">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L53">
-    <cfRule type="containsText" dxfId="42" priority="85" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M53">
-    <cfRule type="containsText" dxfId="41" priority="83" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K53">
-    <cfRule type="colorScale" priority="82">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K53">
-    <cfRule type="containsText" dxfId="40" priority="81" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L54">
-    <cfRule type="colorScale" priority="80">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L54">
-    <cfRule type="containsText" dxfId="39" priority="79" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L55">
-    <cfRule type="colorScale" priority="74">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L55">
-    <cfRule type="containsText" dxfId="36" priority="73" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N55">
-    <cfRule type="colorScale" priority="72">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N55">
-    <cfRule type="containsText" dxfId="35" priority="71" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L56">
-    <cfRule type="colorScale" priority="70">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L56">
-    <cfRule type="containsText" dxfId="34" priority="69" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N56">
-    <cfRule type="colorScale" priority="68">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N56">
-    <cfRule type="containsText" dxfId="33" priority="67" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K56">
-    <cfRule type="colorScale" priority="66">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K56">
-    <cfRule type="containsText" dxfId="32" priority="65" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M56">
-    <cfRule type="colorScale" priority="64">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M56">
-    <cfRule type="containsText" dxfId="31" priority="63" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L58">
-    <cfRule type="colorScale" priority="62">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L58">
-    <cfRule type="containsText" dxfId="30" priority="61" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N58">
-    <cfRule type="colorScale" priority="60">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N58">
-    <cfRule type="containsText" dxfId="29" priority="59" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K65">
-    <cfRule type="colorScale" priority="40">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K65">
-    <cfRule type="containsText" dxfId="28" priority="39" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M58">
-    <cfRule type="colorScale" priority="56">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M58">
-    <cfRule type="containsText" dxfId="27" priority="55" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K66">
-    <cfRule type="colorScale" priority="36">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K60">
-    <cfRule type="containsText" dxfId="26" priority="49" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K66">
-    <cfRule type="containsText" dxfId="24" priority="35" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L63">
-    <cfRule type="containsText" dxfId="22" priority="45" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L65">
-    <cfRule type="colorScale" priority="42">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L65">
-    <cfRule type="containsText" dxfId="19" priority="41" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L66">
-    <cfRule type="colorScale" priority="38">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L66">
-    <cfRule type="containsText" dxfId="17" priority="37" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K73">
-    <cfRule type="containsText" dxfId="13" priority="25" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L73">
-    <cfRule type="colorScale" priority="28">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K73">
-    <cfRule type="colorScale" priority="26">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L73">
-    <cfRule type="containsText" dxfId="12" priority="27" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N73">
+  <conditionalFormatting sqref="L86">
+    <cfRule type="containsText" dxfId="15" priority="29" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K87">
+    <cfRule type="containsText" dxfId="14" priority="21" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L87">
     <cfRule type="colorScale" priority="24">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6852,12 +6823,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N73">
-    <cfRule type="containsText" dxfId="11" priority="23" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L86">
+  <conditionalFormatting sqref="K87">
     <cfRule type="colorScale" priority="22">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6869,17 +6835,46 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L86">
-    <cfRule type="containsText" dxfId="9" priority="21" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K87">
-    <cfRule type="containsText" dxfId="7" priority="13" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="L87">
+    <cfRule type="containsText" dxfId="13" priority="23" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N87">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N87">
+    <cfRule type="containsText" dxfId="12" priority="19" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K88">
+    <cfRule type="containsText" dxfId="11" priority="15" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L88">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K88">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6891,7 +6886,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K87">
+  <conditionalFormatting sqref="L88">
+    <cfRule type="containsText" dxfId="10" priority="17" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N88">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6903,12 +6903,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L87">
-    <cfRule type="containsText" dxfId="6" priority="15" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N87">
+  <conditionalFormatting sqref="N88">
+    <cfRule type="containsText" dxfId="9" priority="13" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M87">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6920,17 +6920,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N87">
-    <cfRule type="containsText" dxfId="5" priority="11" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K88">
-    <cfRule type="containsText" dxfId="4" priority="7" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L88">
+  <conditionalFormatting sqref="M87">
+    <cfRule type="containsText" dxfId="8" priority="11" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M88">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6942,7 +6937,17 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K88">
+  <conditionalFormatting sqref="M88">
+    <cfRule type="containsText" dxfId="7" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K89">
+    <cfRule type="containsText" dxfId="3" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L89">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6954,12 +6959,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L88">
-    <cfRule type="containsText" dxfId="3" priority="9" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N88">
+  <conditionalFormatting sqref="K89">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6971,12 +6971,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N88">
-    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M87">
+  <conditionalFormatting sqref="L89">
+    <cfRule type="containsText" dxfId="2" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N89">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6988,12 +6988,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M87">
+  <conditionalFormatting sqref="N89">
     <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M88">
+  <conditionalFormatting sqref="M89">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -7005,7 +7005,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M88">
+  <conditionalFormatting sqref="M89">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
